--- a/stock.xlsx
+++ b/stock.xlsx
@@ -385,7 +385,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>200</v>
+        <v>966</v>
       </c>
       <c r="D2">
         <v>10</v>
